--- a/service-pack-planning.xlsx
+++ b/service-pack-planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://docs.philips.com/personal/vidya_cen_philips_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ingbtcpic1vwsfs.code1.emi.philips.com\Bangalore3\Projects\DXR\FSA\Service pack planning sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67CF2B1C-E9E8-4D59-A1C2-05057E833611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0519707B-A9B3-4FCF-85E9-1AAA424BEEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2CCB4F40-67F8-46C5-A303-B9EF7566CEAF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{2CCB4F40-67F8-46C5-A303-B9EF7566CEAF}"/>
   </bookViews>
   <sheets>
     <sheet name="service-pack-planning" sheetId="5" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="66">
   <si>
     <t>Q1</t>
   </si>
@@ -169,15 +169,24 @@
     <t>WK 29'2026</t>
   </si>
   <si>
+    <t>Wk 35'2026</t>
+  </si>
+  <si>
+    <t>Wk 36'2026</t>
+  </si>
+  <si>
+    <t>Wk 37'2026</t>
+  </si>
+  <si>
+    <t>Wk 38'2026</t>
+  </si>
+  <si>
+    <t>Wk 39'2026</t>
+  </si>
+  <si>
     <t>LTSC 2021 SP7</t>
   </si>
   <si>
-    <t>Wk 37'2026</t>
-  </si>
-  <si>
-    <t>Wk 39'2026</t>
-  </si>
-  <si>
     <t>Wk 40'2026</t>
   </si>
   <si>
@@ -190,26 +199,53 @@
     <t>Wk 41'2026</t>
   </si>
   <si>
-    <t>WK 43'2026</t>
-  </si>
-  <si>
     <t>LTSC 1607 SP14</t>
   </si>
   <si>
-    <t>Wk 38'2026</t>
-  </si>
-  <si>
     <t>Wk 42'2026</t>
   </si>
   <si>
     <t>WK 45'2026</t>
+  </si>
+  <si>
+    <t>WK 44'2026</t>
+  </si>
+  <si>
+    <t>WK 47'2026</t>
+  </si>
+  <si>
+    <t>WK 48'2026</t>
+  </si>
+  <si>
+    <t>WK 46'2026</t>
+  </si>
+  <si>
+    <t>WK 49'2026</t>
+  </si>
+  <si>
+    <t>WK 50'2026</t>
+  </si>
+  <si>
+    <t>WK 24'2026</t>
+  </si>
+  <si>
+    <t>WK 27'2026</t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>LTSC 1607 SP12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inprogress </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1087,16 +1123,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1040217-8BFB-4679-9378-904E7D620112}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="15.1796875" customWidth="1"/>
+    <col min="3" max="3" width="14.7265625" customWidth="1"/>
+    <col min="4" max="4" width="18.7265625" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1146,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1121,7 +1157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1138,7 +1174,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1160,18 +1196,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC76A50-D982-4BDB-B0D8-5FFC6EE09F33}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" customWidth="1"/>
+    <col min="4" max="5" width="13.7265625" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="7" max="7" width="16.453125" customWidth="1"/>
+    <col min="8" max="8" width="16.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -1194,7 +1230,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1217,7 +1253,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1240,7 +1276,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -1266,7 +1302,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -1290,7 +1326,7 @@
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -1314,7 +1350,7 @@
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -1338,7 +1374,7 @@
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
@@ -1356,7 +1392,7 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
@@ -1380,7 +1416,7 @@
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
@@ -1398,7 +1434,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>38</v>
       </c>
@@ -1422,7 +1458,7 @@
       </c>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>26</v>
       </c>
@@ -1448,19 +1484,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{581F94FF-2C8A-4251-94FC-92472C1A1740}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.54296875" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -1486,7 +1522,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
@@ -1509,7 +1545,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
@@ -1526,7 +1562,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
@@ -1549,7 +1585,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -1566,7 +1602,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>40</v>
       </c>
@@ -1589,7 +1625,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
@@ -1613,21 +1649,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39BD49DA-E025-4C99-9753-C63138AB1885}">
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" customWidth="1"/>
-    <col min="9" max="9" width="27.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" customWidth="1"/>
+    <col min="6" max="6" width="11.26953125" customWidth="1"/>
+    <col min="7" max="7" width="15.1796875" customWidth="1"/>
+    <col min="8" max="8" width="18.26953125" customWidth="1"/>
+    <col min="9" max="9" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -1652,8 +1688,11 @@
       <c r="H1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="14.65">
+      <c r="I1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
@@ -1667,27 +1706,40 @@
         <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" ht="14.65">
+        <v>23</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="G4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
@@ -1695,11 +1747,11 @@
         <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
@@ -1710,7 +1762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -1718,16 +1770,25 @@
         <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:8">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>34</v>
       </c>
@@ -1735,10 +1796,10 @@
         <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>25</v>
@@ -1750,7 +1811,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
@@ -1763,49 +1824,61 @@
       <c r="D8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="E8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1814,20 +1887,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52FECE3C-749C-443D-BB38-B34AFB798837}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18.26953125" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -1849,10 +1922,13 @@
       <c r="G1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>25</v>
@@ -1873,28 +1949,35 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
+        <v>49</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>25</v>
@@ -1915,31 +1998,38 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
+        <v>55</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>25</v>
@@ -1957,24 +2047,31 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1984,21 +2081,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF39F388-4C65-44AE-9227-F01D801D10FC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30d9df97-1706-4bab-bca5-48fb0f30358d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b05385d9-53d8-41a9-b5ab-fe934fad5743" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2011,8 +2102,14 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30d9df97-1706-4bab-bca5-48fb0f30358d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b05385d9-53d8-41a9-b5ab-fe934fad5743" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2205,19 +2302,49 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{105F31ED-B842-489E-B83B-1482223D0D1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{468D0737-806D-4B60-88E0-E7C0AAC59B26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DCC164C-E0EB-4A13-AE86-AFEC8F690DCE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DCC164C-E0EB-4A13-AE86-AFEC8F690DCE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{468D0737-806D-4B60-88E0-E7C0AAC59B26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{105F31ED-B842-489E-B83B-1482223D0D1F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="30d9df97-1706-4bab-bca5-48fb0f30358d"/>
+    <ds:schemaRef ds:uri="b05385d9-53d8-41a9-b5ab-fe934fad5743"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0A665F7-F571-4A50-A037-28440C478248}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0A665F7-F571-4A50-A037-28440C478248}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="30d9df97-1706-4bab-bca5-48fb0f30358d"/>
+    <ds:schemaRef ds:uri="b05385d9-53d8-41a9-b5ab-fe934fad5743"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/service-pack-planning.xlsx
+++ b/service-pack-planning.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ingbtcpic1vwsfs.code1.emi.philips.com\Bangalore3\Projects\DXR\FSA\Service pack planning sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0519707B-A9B3-4FCF-85E9-1AAA424BEEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B6D589-990F-49FF-B4E3-0E9DDC1048B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{2CCB4F40-67F8-46C5-A303-B9EF7566CEAF}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="65">
   <si>
     <t>Q1</t>
   </si>
@@ -178,45 +178,24 @@
     <t>Wk 37'2026</t>
   </si>
   <si>
-    <t>Wk 38'2026</t>
-  </si>
-  <si>
-    <t>Wk 39'2026</t>
-  </si>
-  <si>
-    <t>LTSC 2021 SP7</t>
-  </si>
-  <si>
     <t>Wk 40'2026</t>
   </si>
   <si>
-    <t>WK 42'2026</t>
-  </si>
-  <si>
     <t>LTSC 1809 SP5</t>
   </si>
   <si>
     <t>Wk 41'2026</t>
   </si>
   <si>
-    <t>LTSC 1607 SP14</t>
-  </si>
-  <si>
     <t>Wk 42'2026</t>
   </si>
   <si>
-    <t>WK 45'2026</t>
-  </si>
-  <si>
     <t>WK 44'2026</t>
   </si>
   <si>
     <t>WK 47'2026</t>
   </si>
   <si>
-    <t>WK 48'2026</t>
-  </si>
-  <si>
     <t>WK 46'2026</t>
   </si>
   <si>
@@ -239,6 +218,24 @@
   </si>
   <si>
     <t xml:space="preserve">Inprogress </t>
+  </si>
+  <si>
+    <t>WK 53'2026</t>
+  </si>
+  <si>
+    <t>WK 51'2026</t>
+  </si>
+  <si>
+    <t>Wk 48'2026</t>
+  </si>
+  <si>
+    <t>Wk 47'2026</t>
+  </si>
+  <si>
+    <t>Wk 44'2026</t>
+  </si>
+  <si>
+    <t>Wk 45'2026</t>
   </si>
 </sst>
 </file>
@@ -1649,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39BD49DA-E025-4C99-9753-C63138AB1885}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.81640625" customWidth="1"/>
@@ -1689,7 +1686,7 @@
         <v>28</v>
       </c>
       <c r="I1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -1712,19 +1709,19 @@
         <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>41</v>
@@ -1741,7 +1738,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>23</v>
@@ -1756,10 +1753,10 @@
         <v>25</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -1767,30 +1764,30 @@
         <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>23</v>
@@ -1799,16 +1796,16 @@
         <v>23</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -1818,65 +1815,16 @@
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="2" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1923,18 +1871,18 @@
         <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>25</v>
@@ -1957,7 +1905,7 @@
         <v>44</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>48</v>
@@ -1966,18 +1914,18 @@
         <v>49</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>25</v>
@@ -2006,27 +1954,27 @@
         <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>25</v>
@@ -2055,22 +2003,22 @@
         <v>44</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="F8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2089,11 +2037,6 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
@@ -2101,7 +2044,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="30d9df97-1706-4bab-bca5-48fb0f30358d">
@@ -2112,7 +2055,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F9531C6DA629D4C8FCD52754E4B46E3" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c5616788a33f9994cceaf7133eeb7f3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30d9df97-1706-4bab-bca5-48fb0f30358d" xmlns:ns3="b05385d9-53d8-41a9-b5ab-fe934fad5743" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6f7eb6ccdbb53bc557ecb725567e0585" ns2:_="" ns3:_="">
     <xsd:import namespace="30d9df97-1706-4bab-bca5-48fb0f30358d"/>
@@ -2301,15 +2244,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{468D0737-806D-4B60-88E0-E7C0AAC59B26}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DCC164C-E0EB-4A13-AE86-AFEC8F690DCE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -2317,7 +2257,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{105F31ED-B842-489E-B83B-1482223D0D1F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2328,7 +2268,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0A665F7-F571-4A50-A037-28440C478248}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2347,6 +2287,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{468D0737-806D-4B60-88E0-E7C0AAC59B26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{1a407a2d-7675-4d17-8692-b3ac285306e4}" enabled="0" method="" siteId="{1a407a2d-7675-4d17-8692-b3ac285306e4}" removed="1"/>
